--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7323F022-B28E-40FD-A356-5E718FBD49B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81BF7C-242E-4F60-900F-04ADF033ED40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -416,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -427,28 +427,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -456,23 +448,23 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>12</v>
@@ -480,25 +472,33 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F81BF7C-242E-4F60-900F-04ADF033ED40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A9D037-E800-40B1-B33E-AC57A4E596D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="62100" yWindow="2895" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1"/>
@@ -83,6 +83,37 @@
   <si>
     <t>Value</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PS1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PS2</t>
+  </si>
+  <si>
+    <t>PS3</t>
+  </si>
+  <si>
+    <t>PS4</t>
+  </si>
+  <si>
+    <t>PS5</t>
+  </si>
+  <si>
+    <t>PS6</t>
+  </si>
+  <si>
+    <t>PS7</t>
+  </si>
+  <si>
+    <t>PS8</t>
+  </si>
+  <si>
+    <t>Export Time</t>
+  </si>
+  <si>
+    <t>2026/9/30 9:38:24</t>
   </si>
 </sst>
 </file>
@@ -416,15 +447,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A2:C21"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.4">
@@ -440,15 +475,18 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -456,23 +494,23 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
@@ -480,25 +518,97 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
     </row>

--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A9D037-E800-40B1-B33E-AC57A4E596D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D38629-1FFB-4564-BAC5-31EF60223F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="62100" yWindow="2895" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="61980" yWindow="3585" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1"/>
@@ -114,13 +114,21 @@
   </si>
   <si>
     <t>2026/9/30 9:38:24</t>
+  </si>
+  <si>
+    <t>ConfigURL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://serial-app.vercel.app/config/default.xlsx</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +149,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -159,16 +175,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -447,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C21"/>
+  <dimension ref="A2:C22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
@@ -475,26 +494,29 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
-        <v>1</v>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -502,23 +524,23 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
@@ -526,39 +548,39 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
@@ -566,23 +588,23 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -590,30 +612,41 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12D38629-1FFB-4564-BAC5-31EF60223F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8977B2-E018-4F18-AB13-C7B4BB15604B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="61980" yWindow="3585" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30090" yWindow="4515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1"/>
@@ -121,6 +132,22 @@
   </si>
   <si>
     <t>https://serial-app.vercel.app/config/default.xlsx</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Regex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>^[A-Z0-9.=]+$</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>^[A-Z0-9=]{12}$</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>^[0-9]{8}$</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -466,14 +493,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:C22"/>
+  <dimension ref="A2:D22"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -481,7 +510,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -491,8 +520,11 @@
       <c r="C4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -503,7 +535,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -514,7 +546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -522,7 +554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -530,31 +562,40 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -562,7 +603,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -570,7 +611,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -578,7 +619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -586,7 +627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>16</v>
       </c>

--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8977B2-E018-4F18-AB13-C7B4BB15604B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960D2787-2FCA-4C2D-AF48-F0FFA70A0318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30090" yWindow="4515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -493,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
@@ -502,53 +502,61 @@
     <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B1" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
+      <c r="C5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -556,72 +564,72 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>12</v>
@@ -629,23 +637,23 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -653,40 +661,32 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960D2787-2FCA-4C2D-AF48-F0FFA70A0318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A69F19-C0A5-4989-AAAF-85D43A9CF445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="59970" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1"/>
@@ -148,6 +148,10 @@
   </si>
   <si>
     <t>^[0-9]{8}$</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>A:QR</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -493,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
@@ -504,124 +508,128 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>12</v>
@@ -629,23 +637,23 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>12</v>
@@ -653,40 +661,32 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/config/default.xlsx
+++ b/public/config/default.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IKEGAMI\JAVAscript\SerialRecoder\serial-app\public\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A69F19-C0A5-4989-AAAF-85D43A9CF445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92600508-93B6-463A-A3D2-FD4AE27BC200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59970" yWindow="1770" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57495" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -502,8 +502,8 @@
   <cols>
     <col min="1" max="1" width="11.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -514,10 +514,10 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
         <v>14</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.4">
@@ -525,7 +525,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>26</v>
       </c>
     </row>
@@ -533,7 +533,7 @@
       <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
     </row>
@@ -542,7 +542,7 @@
         <v>0</v>
       </c>
       <c r="B4" s="1"/>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -569,7 +569,7 @@
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="C7" t="s">
         <v>28</v>
       </c>
     </row>
@@ -580,7 +580,7 @@
       <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D8" t="s">
+      <c r="C8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -591,7 +591,7 @@
       <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -686,7 +686,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{D9E34957-D486-4A13-9044-4494FDBFBD22}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
